--- a/协作/20-验收记录.xlsx
+++ b/协作/20-验收记录.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -643,9 +643,73 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>验收-0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>切片-0003</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>验收-0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>切片-0003</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>证据-0010</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="C2:C121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="C2:C121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"passed,blocked"</formula1>
     </dataValidation>
   </dataValidations>
@@ -704,10 +768,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="B2:B121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"致命,严重,一般,建议"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="F2:F121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待修,修复中,待验证,已关闭,不接受"</formula1>
     </dataValidation>
   </dataValidations>

--- a/协作/20-验收记录.xlsx
+++ b/协作/20-验收记录.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -704,6 +704,38 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>验收-0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>切片-0003</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>证据-0011</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-10-18 03:15:00 +08:00</t>
         </is>
       </c>
     </row>

--- a/协作/20-验收记录.xlsx
+++ b/协作/20-验收记录.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -736,6 +736,38 @@
       <c r="G8" t="inlineStr">
         <is>
           <t>2026-10-18 03:15:00 +08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>验收-0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>切片-0004</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>证据-0012</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-10-18 03:45:00 +08:00</t>
         </is>
       </c>
     </row>

--- a/协作/20-验收记录.xlsx
+++ b/协作/20-验收记录.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -768,6 +768,38 @@
       <c r="G9" t="inlineStr">
         <is>
           <t>2026-10-18 03:45:00 +08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>验收-0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>切片-0005</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>证据-0014</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:20:00 +08:00</t>
         </is>
       </c>
     </row>

--- a/协作/20-验收记录.xlsx
+++ b/协作/20-验收记录.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -800,6 +800,38 @@
       <c r="G10" t="inlineStr">
         <is>
           <t>2026-10-18 04:20:00 +08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>验收-0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>切片-0006</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>证据-0015</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:40:00 +08:00</t>
         </is>
       </c>
     </row>

--- a/协作/20-验收记录.xlsx
+++ b/协作/20-验收记录.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -832,6 +832,38 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>2026-10-18 04:40:00 +08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>验收-0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>切片-0007</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>证据-0016</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:55:00 +08:00</t>
         </is>
       </c>
     </row>
